--- a/artfynd/A 33191-2021 artfynd.xlsx
+++ b/artfynd/A 33191-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 33191-2021 artfynd.xlsx
+++ b/artfynd/A 33191-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -785,6 +785,782 @@
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>130564762</v>
+      </c>
+      <c r="B3" t="n">
+        <v>8440</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Söderby, Srm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>621313</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6594764</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Överselö</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>130564759</v>
+      </c>
+      <c r="B4" t="n">
+        <v>5177</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Söderby, Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>621428</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6594408</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Överselö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>130563202</v>
+      </c>
+      <c r="B5" t="n">
+        <v>101112</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Söderby, Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>621458</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6594414</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Överselö</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>130563203</v>
+      </c>
+      <c r="B6" t="n">
+        <v>92184</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Söderby, Srm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>621455</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6594412</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Överselö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>130564232</v>
+      </c>
+      <c r="B7" t="n">
+        <v>91731</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Söderby, Srm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>621446</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6594422</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Överselö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Mårten Wikström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>130564233</v>
+      </c>
+      <c r="B8" t="n">
+        <v>92184</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Söderby, Srm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>621445</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6594425</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Överselö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Mårten Wikström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>130564758</v>
+      </c>
+      <c r="B9" t="n">
+        <v>91731</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Söderby, Srm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>621441</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6594406</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Överselö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>130564754</v>
+      </c>
+      <c r="B10" t="n">
+        <v>8440</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Söderby, Srm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>621462</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6594298</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Överselö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33191-2021 artfynd.xlsx
+++ b/artfynd/A 33191-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1561,6 +1561,123 @@
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>130593889</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57772</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100067</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Havsörn</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Haliaeetus albicilla</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Söderby, Srm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>621610</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6594415</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Överselö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Honan från det adulta paret landade i en tall ungefär här</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Mårten Wikström</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33191-2021 artfynd.xlsx
+++ b/artfynd/A 33191-2021 artfynd.xlsx
@@ -1078,32 +1078,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130563203</v>
+        <v>130564232</v>
       </c>
       <c r="B6" t="n">
-        <v>92184</v>
+        <v>91731</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>621455</v>
+        <v>621446</v>
       </c>
       <c r="R6" t="n">
-        <v>6594412</v>
+        <v>6594422</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1168,39 +1168,39 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Mårten Wikström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130564232</v>
+        <v>130563203</v>
       </c>
       <c r="B7" t="n">
-        <v>91731</v>
+        <v>92184</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1210,10 +1210,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>621446</v>
+        <v>621455</v>
       </c>
       <c r="R7" t="n">
-        <v>6594422</v>
+        <v>6594412</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1265,7 +1265,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Mårten Wikström</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 33191-2021 artfynd.xlsx
+++ b/artfynd/A 33191-2021 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130564762</v>
+        <v>130564759</v>
       </c>
       <c r="B3" t="n">
-        <v>8440</v>
+        <v>5177</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106554</v>
+        <v>100526</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>621313</v>
+        <v>621428</v>
       </c>
       <c r="R3" t="n">
-        <v>6594764</v>
+        <v>6594408</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130564759</v>
+        <v>130564762</v>
       </c>
       <c r="B4" t="n">
-        <v>5177</v>
+        <v>8440</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>106554</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>621428</v>
+        <v>621313</v>
       </c>
       <c r="R4" t="n">
-        <v>6594408</v>
+        <v>6594764</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -984,7 +984,7 @@
         <v>130563202</v>
       </c>
       <c r="B5" t="n">
-        <v>101112</v>
+        <v>101138</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>130564232</v>
       </c>
       <c r="B6" t="n">
-        <v>91731</v>
+        <v>91757</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>130563203</v>
       </c>
       <c r="B7" t="n">
-        <v>92184</v>
+        <v>92210</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>130564233</v>
       </c>
       <c r="B8" t="n">
-        <v>92184</v>
+        <v>92210</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>130564758</v>
       </c>
       <c r="B9" t="n">
-        <v>91731</v>
+        <v>91757</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>130593889</v>
       </c>
       <c r="B11" t="n">
-        <v>57772</v>
+        <v>57798</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 33191-2021 artfynd.xlsx
+++ b/artfynd/A 33191-2021 artfynd.xlsx
@@ -984,7 +984,7 @@
         <v>130563202</v>
       </c>
       <c r="B5" t="n">
-        <v>101138</v>
+        <v>101139</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>130564232</v>
       </c>
       <c r="B6" t="n">
-        <v>91757</v>
+        <v>91758</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>130563203</v>
       </c>
       <c r="B7" t="n">
-        <v>92210</v>
+        <v>92211</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>130564233</v>
       </c>
       <c r="B8" t="n">
-        <v>92210</v>
+        <v>92211</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>130564758</v>
       </c>
       <c r="B9" t="n">
-        <v>91757</v>
+        <v>91758</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 33191-2021 artfynd.xlsx
+++ b/artfynd/A 33191-2021 artfynd.xlsx
@@ -984,7 +984,7 @@
         <v>130563202</v>
       </c>
       <c r="B5" t="n">
-        <v>101139</v>
+        <v>101140</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>130564232</v>
       </c>
       <c r="B6" t="n">
-        <v>91758</v>
+        <v>91759</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>130563203</v>
       </c>
       <c r="B7" t="n">
-        <v>92211</v>
+        <v>92212</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>130564233</v>
       </c>
       <c r="B8" t="n">
-        <v>92211</v>
+        <v>92212</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>130564758</v>
       </c>
       <c r="B9" t="n">
-        <v>91758</v>
+        <v>91759</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 33191-2021 artfynd.xlsx
+++ b/artfynd/A 33191-2021 artfynd.xlsx
@@ -984,7 +984,7 @@
         <v>130563202</v>
       </c>
       <c r="B5" t="n">
-        <v>101140</v>
+        <v>101142</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1078,32 +1078,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130564232</v>
+        <v>130563203</v>
       </c>
       <c r="B6" t="n">
-        <v>91759</v>
+        <v>92214</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>621446</v>
+        <v>621455</v>
       </c>
       <c r="R6" t="n">
-        <v>6594422</v>
+        <v>6594412</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1168,39 +1168,39 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Mårten Wikström</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130563203</v>
+        <v>130564232</v>
       </c>
       <c r="B7" t="n">
-        <v>92212</v>
+        <v>91761</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1210,10 +1210,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>621455</v>
+        <v>621446</v>
       </c>
       <c r="R7" t="n">
-        <v>6594412</v>
+        <v>6594422</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1265,7 +1265,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Mårten Wikström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1275,7 +1275,7 @@
         <v>130564233</v>
       </c>
       <c r="B8" t="n">
-        <v>92212</v>
+        <v>92214</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>130564758</v>
       </c>
       <c r="B9" t="n">
-        <v>91759</v>
+        <v>91761</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>130593889</v>
       </c>
       <c r="B11" t="n">
-        <v>57798</v>
+        <v>57800</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 33191-2021 artfynd.xlsx
+++ b/artfynd/A 33191-2021 artfynd.xlsx
@@ -984,7 +984,7 @@
         <v>130563202</v>
       </c>
       <c r="B5" t="n">
-        <v>101142</v>
+        <v>101146</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1078,32 +1078,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130563203</v>
+        <v>130564232</v>
       </c>
       <c r="B6" t="n">
-        <v>92214</v>
+        <v>91761</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>621455</v>
+        <v>621446</v>
       </c>
       <c r="R6" t="n">
-        <v>6594412</v>
+        <v>6594422</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1168,39 +1168,39 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Mårten Wikström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130564232</v>
+        <v>130563203</v>
       </c>
       <c r="B7" t="n">
-        <v>91761</v>
+        <v>92220</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1210,10 +1210,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>621446</v>
+        <v>621455</v>
       </c>
       <c r="R7" t="n">
-        <v>6594422</v>
+        <v>6594412</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1265,7 +1265,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Mårten Wikström</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1275,7 +1275,7 @@
         <v>130564233</v>
       </c>
       <c r="B8" t="n">
-        <v>92214</v>
+        <v>92220</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 33191-2021 artfynd.xlsx
+++ b/artfynd/A 33191-2021 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130564759</v>
+        <v>130564762</v>
       </c>
       <c r="B3" t="n">
-        <v>5177</v>
+        <v>8440</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100526</v>
+        <v>106554</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>621428</v>
+        <v>621313</v>
       </c>
       <c r="R3" t="n">
-        <v>6594408</v>
+        <v>6594764</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130564762</v>
+        <v>130564759</v>
       </c>
       <c r="B4" t="n">
-        <v>8440</v>
+        <v>5177</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106554</v>
+        <v>100526</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>621313</v>
+        <v>621428</v>
       </c>
       <c r="R4" t="n">
-        <v>6594764</v>
+        <v>6594408</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>

--- a/artfynd/A 33191-2021 artfynd.xlsx
+++ b/artfynd/A 33191-2021 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130564762</v>
+        <v>130564759</v>
       </c>
       <c r="B3" t="n">
-        <v>8440</v>
+        <v>5177</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106554</v>
+        <v>100526</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>621313</v>
+        <v>621428</v>
       </c>
       <c r="R3" t="n">
-        <v>6594764</v>
+        <v>6594408</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130564759</v>
+        <v>130564762</v>
       </c>
       <c r="B4" t="n">
-        <v>5177</v>
+        <v>8440</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>106554</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>621428</v>
+        <v>621313</v>
       </c>
       <c r="R4" t="n">
-        <v>6594408</v>
+        <v>6594764</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>

--- a/artfynd/A 33191-2021 artfynd.xlsx
+++ b/artfynd/A 33191-2021 artfynd.xlsx
@@ -984,7 +984,7 @@
         <v>130563202</v>
       </c>
       <c r="B5" t="n">
-        <v>101146</v>
+        <v>101159</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>130564232</v>
       </c>
       <c r="B6" t="n">
-        <v>91761</v>
+        <v>91774</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>130563203</v>
       </c>
       <c r="B7" t="n">
-        <v>92220</v>
+        <v>92233</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>130564233</v>
       </c>
       <c r="B8" t="n">
-        <v>92220</v>
+        <v>92233</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>130564758</v>
       </c>
       <c r="B9" t="n">
-        <v>91761</v>
+        <v>91774</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>130593889</v>
       </c>
       <c r="B11" t="n">
-        <v>57800</v>
+        <v>57808</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 33191-2021 artfynd.xlsx
+++ b/artfynd/A 33191-2021 artfynd.xlsx
@@ -984,7 +984,7 @@
         <v>130563202</v>
       </c>
       <c r="B5" t="n">
-        <v>101159</v>
+        <v>101160</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>130564232</v>
       </c>
       <c r="B6" t="n">
-        <v>91774</v>
+        <v>91775</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>130563203</v>
       </c>
       <c r="B7" t="n">
-        <v>92233</v>
+        <v>92234</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>130564233</v>
       </c>
       <c r="B8" t="n">
-        <v>92233</v>
+        <v>92234</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>130564758</v>
       </c>
       <c r="B9" t="n">
-        <v>91774</v>
+        <v>91775</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>130593889</v>
       </c>
       <c r="B11" t="n">
-        <v>57808</v>
+        <v>57809</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 33191-2021 artfynd.xlsx
+++ b/artfynd/A 33191-2021 artfynd.xlsx
@@ -984,7 +984,7 @@
         <v>130563202</v>
       </c>
       <c r="B5" t="n">
-        <v>101160</v>
+        <v>101163</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1078,32 +1078,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130564232</v>
+        <v>130563203</v>
       </c>
       <c r="B6" t="n">
-        <v>91775</v>
+        <v>92235</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>621446</v>
+        <v>621455</v>
       </c>
       <c r="R6" t="n">
-        <v>6594422</v>
+        <v>6594412</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1168,39 +1168,39 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Mårten Wikström</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130563203</v>
+        <v>130564232</v>
       </c>
       <c r="B7" t="n">
-        <v>92234</v>
+        <v>91776</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1210,10 +1210,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>621455</v>
+        <v>621446</v>
       </c>
       <c r="R7" t="n">
-        <v>6594412</v>
+        <v>6594422</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1265,7 +1265,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Mårten Wikström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1275,7 +1275,7 @@
         <v>130564233</v>
       </c>
       <c r="B8" t="n">
-        <v>92234</v>
+        <v>92235</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>130564758</v>
       </c>
       <c r="B9" t="n">
-        <v>91775</v>
+        <v>91776</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>130593889</v>
       </c>
       <c r="B11" t="n">
-        <v>57809</v>
+        <v>57810</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 33191-2021 artfynd.xlsx
+++ b/artfynd/A 33191-2021 artfynd.xlsx
@@ -1078,32 +1078,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130563203</v>
+        <v>130564232</v>
       </c>
       <c r="B6" t="n">
-        <v>92235</v>
+        <v>91776</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>621455</v>
+        <v>621446</v>
       </c>
       <c r="R6" t="n">
-        <v>6594412</v>
+        <v>6594422</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1168,39 +1168,39 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Mårten Wikström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130564232</v>
+        <v>130563203</v>
       </c>
       <c r="B7" t="n">
-        <v>91776</v>
+        <v>92235</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1210,10 +1210,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>621446</v>
+        <v>621455</v>
       </c>
       <c r="R7" t="n">
-        <v>6594422</v>
+        <v>6594412</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1265,7 +1265,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Mårten Wikström</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 33191-2021 artfynd.xlsx
+++ b/artfynd/A 33191-2021 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130564762</v>
+        <v>130564759</v>
       </c>
       <c r="B3" t="n">
-        <v>8440</v>
+        <v>5177</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106554</v>
+        <v>100526</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>621313</v>
+        <v>621428</v>
       </c>
       <c r="R3" t="n">
-        <v>6594764</v>
+        <v>6594408</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130564759</v>
+        <v>130564762</v>
       </c>
       <c r="B4" t="n">
-        <v>5177</v>
+        <v>8440</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>106554</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>621428</v>
+        <v>621313</v>
       </c>
       <c r="R4" t="n">
-        <v>6594408</v>
+        <v>6594764</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -984,7 +984,7 @@
         <v>130563202</v>
       </c>
       <c r="B5" t="n">
-        <v>101163</v>
+        <v>101177</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>130564232</v>
       </c>
       <c r="B6" t="n">
-        <v>91776</v>
+        <v>91784</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
         <v>130563203</v>
       </c>
       <c r="B7" t="n">
-        <v>92235</v>
+        <v>92243</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>130564233</v>
       </c>
       <c r="B8" t="n">
-        <v>92235</v>
+        <v>92243</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>130564758</v>
       </c>
       <c r="B9" t="n">
-        <v>91776</v>
+        <v>91784</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 33191-2021 artfynd.xlsx
+++ b/artfynd/A 33191-2021 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130564759</v>
+        <v>130564762</v>
       </c>
       <c r="B3" t="n">
-        <v>5177</v>
+        <v>8440</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100526</v>
+        <v>106554</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>621428</v>
+        <v>621313</v>
       </c>
       <c r="R3" t="n">
-        <v>6594408</v>
+        <v>6594764</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130564762</v>
+        <v>130564759</v>
       </c>
       <c r="B4" t="n">
-        <v>8440</v>
+        <v>5177</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106554</v>
+        <v>100526</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>621313</v>
+        <v>621428</v>
       </c>
       <c r="R4" t="n">
-        <v>6594764</v>
+        <v>6594408</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -984,7 +984,7 @@
         <v>130563202</v>
       </c>
       <c r="B5" t="n">
-        <v>101177</v>
+        <v>101191</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 33191-2021 artfynd.xlsx
+++ b/artfynd/A 33191-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,57 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>112548847</v>
+        <v>130564232</v>
       </c>
       <c r="B2" t="n">
-        <v>93432</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2671</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lindö, Srm</t>
+          <t>Söderby, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>621537</v>
+        <v>621446</v>
       </c>
       <c r="R2" t="n">
-        <v>6594780</v>
+        <v>6594422</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,17 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-10-05</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-10-05</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På stenblock</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -768,51 +754,50 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Amanda Lidén</t>
+          <t>Johan Kjetselberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Amanda Lidén</t>
+          <t>Mårten Wikström</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130564762</v>
+        <v>130564758</v>
       </c>
       <c r="B3" t="n">
-        <v>8440</v>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106554</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>621313</v>
+        <v>621441</v>
       </c>
       <c r="R3" t="n">
-        <v>6594764</v>
+        <v>6594406</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -884,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130564759</v>
+        <v>130563203</v>
       </c>
       <c r="B4" t="n">
-        <v>5177</v>
+        <v>92369</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>621428</v>
+        <v>621455</v>
       </c>
       <c r="R4" t="n">
-        <v>6594408</v>
+        <v>6594412</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -974,39 +959,39 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Samuel Persson</t>
+          <t>Elias Blad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130563202</v>
+        <v>130564233</v>
       </c>
       <c r="B5" t="n">
-        <v>101215</v>
+        <v>92369</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>1209</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1016,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>621458</v>
+        <v>621445</v>
       </c>
       <c r="R5" t="n">
-        <v>6594414</v>
+        <v>6594425</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1071,55 +1056,59 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Mårten Wikström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130564232</v>
+        <v>112548847</v>
       </c>
       <c r="B6" t="n">
-        <v>91808</v>
+        <v>96426</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>2671</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Söderby, Srm</t>
+          <t>Lindö, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>621446</v>
+        <v>621537</v>
       </c>
       <c r="R6" t="n">
-        <v>6594422</v>
+        <v>6594780</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1143,12 +1132,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2023-10-05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2023-10-05</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På stenblock</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1157,63 +1151,79 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Amanda Lidén</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Mårten Wikström</t>
+          <t>Amanda Lidén</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130563203</v>
+        <v>130593889</v>
       </c>
       <c r="B7" t="n">
-        <v>92267</v>
+        <v>57899</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1209</v>
+        <v>100067</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Söderby, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>621455</v>
+        <v>621610</v>
       </c>
       <c r="R7" t="n">
-        <v>6594412</v>
+        <v>6594415</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1240,12 +1250,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-03-06</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Honan från det adulta paret landade i en tall ungefär här</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1260,44 +1275,44 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Johan Kjetselberg</t>
+          <t>Samuel Persson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Elias Blad</t>
+          <t>Mårten Wikström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130564233</v>
+        <v>130564759</v>
       </c>
       <c r="B8" t="n">
-        <v>92267</v>
+        <v>5179</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1209</v>
+        <v>100526</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1307,10 +1322,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>621445</v>
+        <v>621428</v>
       </c>
       <c r="R8" t="n">
-        <v>6594425</v>
+        <v>6594408</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1362,39 +1377,39 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Mårten Wikström</t>
+          <t>Samuel Persson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130564758</v>
+        <v>130564754</v>
       </c>
       <c r="B9" t="n">
-        <v>91808</v>
+        <v>8444</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>106554</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1404,10 +1419,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>621441</v>
+        <v>621462</v>
       </c>
       <c r="R9" t="n">
-        <v>6594406</v>
+        <v>6594298</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1466,10 +1481,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130564754</v>
+        <v>130564762</v>
       </c>
       <c r="B10" t="n">
-        <v>8440</v>
+        <v>8444</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1501,10 +1516,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>621462</v>
+        <v>621313</v>
       </c>
       <c r="R10" t="n">
-        <v>6594298</v>
+        <v>6594764</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1563,60 +1578,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130593889</v>
+        <v>130564771</v>
       </c>
       <c r="B11" t="n">
-        <v>57830</v>
+        <v>99153</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100067</v>
+        <v>219874</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Söderby, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>621610</v>
+        <v>621274</v>
       </c>
       <c r="R11" t="n">
-        <v>6594415</v>
+        <v>6594753</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1643,17 +1643,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Honan från det adulta paret landade i en tall ungefär här</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1668,15 +1663,306 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
           <t>Samuel Persson</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>Mårten Wikström</t>
-        </is>
-      </c>
       <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>130564774</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99153</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Söderby, Srm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>621273</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6594721</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Överselö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>130564751</v>
+      </c>
+      <c r="B13" t="n">
+        <v>102559</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>222133</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Jungfrulin</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Polygala vulgaris</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Söderby, Srm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>621461</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6594254</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Överselö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Samuel Persson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>130563202</v>
+      </c>
+      <c r="B14" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Söderby, Srm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>621458</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6594414</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Strängnäs</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Överselö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Johan Kjetselberg</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Elias Blad</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
